--- a/Risk_Register/Website-Cybersecurity-Risk-Register.xlsx
+++ b/Risk_Register/Website-Cybersecurity-Risk-Register.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JOB\INTERVIEW PREP\sweet_sin\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JOB\INTERVIEW PREP\sweet_sin\Dany\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23BE8BAF-3485-4B12-8432-C7F0C9940B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB0B630B-208A-4757-B681-235F30C60F76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1848" yWindow="1848" windowWidth="17280" windowHeight="9420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Executive Summary" sheetId="1" r:id="rId1"/>
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="265">
   <si>
     <t>Website Cybersecurity Risk Assessment</t>
   </si>
@@ -857,6 +857,36 @@
   </si>
   <si>
     <t xml:space="preserve">P2 - High priority </t>
+  </si>
+  <si>
+    <t>AS-09</t>
+  </si>
+  <si>
+    <t>Supports access to the website and delivery of services to legitimate users.</t>
+  </si>
+  <si>
+    <t>Availability, integrity, resilience</t>
+  </si>
+  <si>
+    <t>Website downtime, service disruption, or inability for customers to access the service.</t>
+  </si>
+  <si>
+    <t>AS-10</t>
+  </si>
+  <si>
+    <t>HTTP security configuration and TLS certificates</t>
+  </si>
+  <si>
+    <t>Supports secure browser connections and defines website security-related response headers.</t>
+  </si>
+  <si>
+    <t>Confidentiality, integrity, authenticity</t>
+  </si>
+  <si>
+    <t>Weakened connection security, reduced browser-side protection, or increased exposure to certain web attacks.</t>
+  </si>
+  <si>
+    <t>Website availability and network facing services</t>
   </si>
 </sst>
 </file>
@@ -953,7 +983,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -985,6 +1015,13 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2661,7 +2698,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2824,6 +2861,50 @@
         <v>253</v>
       </c>
     </row>
+    <row r="10" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="E11" s="14"/>
+    </row>
+    <row r="12" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="E13" s="14"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E9" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
